--- a/docs/08-reports/test-reports/Report5.2_Integration_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.2_Integration_Test.xlsx
@@ -1416,7 +1416,7 @@
         <v>Issue Date</v>
       </c>
       <c r="F5" s="14" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="32" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="B12" s="26" t="str">
         <v>1.1</v>
@@ -1654,7 +1654,7 @@
         <v>M</v>
       </c>
       <c r="E12" s="33" t="str">
-        <v>Regenerate: 1099 xUnit methods</v>
+        <v>Regenerate: 1129 xUnit methods</v>
       </c>
       <c r="F12" s="34" t="str"/>
       <c r="G12" s="31"/>
@@ -2654,7 +2654,7 @@
         <v>Number of TCs</v>
       </c>
       <c r="B4" s="111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -2726,19 +2726,19 @@
         <v>Round 1</v>
       </c>
       <c r="B6" s="115" t="n">
-        <f>COUNTIF(F12:F37,"Passed")</f>
+        <f>COUNTIF(F12:F39,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C6" s="115" t="n">
-        <f>COUNTIF(F12:F37,"Failed")</f>
+        <f>COUNTIF(F12:F39,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D6" s="115" t="n">
         <f>B4-B6-C6-E6</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="115" t="n">
-        <f>COUNTIF(F12:F37,"Skipped")</f>
+        <f>COUNTIF(F12:F39,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F6" s="108"/>
@@ -2767,19 +2767,19 @@
         <v>Round 2</v>
       </c>
       <c r="B7" s="115" t="n">
-        <f>COUNTIF(I12:I37,"Passed")</f>
+        <f>COUNTIF(I12:I39,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C7" s="115" t="n">
-        <f>COUNTIF(I12:I37,"Failed")</f>
+        <f>COUNTIF(I12:I39,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D7" s="115" t="n">
         <f>B4-B7-C7-E7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="115" t="n">
-        <f>COUNTIF(I12:I37,"Skipped")</f>
+        <f>COUNTIF(I12:I39,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F7" s="108"/>
@@ -2808,19 +2808,19 @@
         <v>Round 3</v>
       </c>
       <c r="B8" s="115" t="n">
-        <f>COUNTIF(L12:L37,"Passed")</f>
+        <f>COUNTIF(L12:L39,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C8" s="115" t="n">
-        <f>COUNTIF(L12:L37,"Failed")</f>
+        <f>COUNTIF(L12:L39,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D8" s="115" t="n">
         <f>B4-B8-C8-E8</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="115" t="n">
-        <f>COUNTIF(L12:L37,"Skipped")</f>
+        <f>COUNTIF(L12:L39,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F8" s="108"/>
@@ -3937,8 +3937,82 @@
       <c r="X37" s="113"/>
       <c r="Y37" s="113"/>
     </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="121" t="str">
+        <v>Tạo cuộc họp</v>
+      </c>
+      <c r="B38" s="121"/>
+      <c r="C38" s="121"/>
+      <c r="D38" s="121"/>
+      <c r="E38" s="121"/>
+      <c r="F38" s="121"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="121"/>
+      <c r="I38" s="121"/>
+      <c r="J38" s="122"/>
+      <c r="K38" s="121"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="122"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="123"/>
+      <c r="P38" s="124"/>
+      <c r="Q38" s="113"/>
+      <c r="R38" s="113"/>
+      <c r="S38" s="113"/>
+      <c r="T38" s="113"/>
+      <c r="U38" s="113"/>
+      <c r="V38" s="113"/>
+      <c r="W38" s="113"/>
+      <c r="X38" s="113"/>
+      <c r="Y38" s="113"/>
+    </row>
+    <row r="39" ht="167.5" customHeight="1">
+      <c r="A39" s="121" t="str">
+        <v>MEET_FT18</v>
+      </c>
+      <c r="B39" s="121" t="str">
+        <v>Pick the date and times with the date and time fields.</v>
+      </c>
+      <c r="C39" s="121" t="str">
+        <v>1. Open "Tạo cuộc họp".
+2. In Ngày họp type 15/11/2026, then use "Chọn ngày trên lịch" to pick another day.
+3. In Bắt đầu type 09:00, then open "Chọn giờ" and pick 09:30.
+4. Open the list of Kết thúc.
+5. Change Hình thức between Trực tiếp, Trực tuyến and Kết hợp.</v>
+      </c>
+      <c r="D39" s="121" t="str">
+        <v>1. Dates read dd/mm/yyyy and times hh:mm on the 24-hour clock, whatever the browser language.
+2. The end-time list starts after the start time and shows how long the meeting would last.
+3. Under Hình thức the hint says how it is recorded: "Ghi âm: Thư ký ghi cả phòng.", "Ghi âm: mỗi người ghi micro của mình." or "Ghi âm: mic phòng và micro người trực tuyến.".</v>
+      </c>
+      <c r="E39" s="121" t="str">
+        <v>1. Signed in as thuky@trustcabinet.local.</v>
+      </c>
+      <c r="F39" s="121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G39" s="122" t="str"/>
+      <c r="H39" s="121" t="str"/>
+      <c r="I39" s="121" t="str"/>
+      <c r="J39" s="122" t="str"/>
+      <c r="K39" s="121" t="str"/>
+      <c r="L39" s="121" t="str"/>
+      <c r="M39" s="122" t="str"/>
+      <c r="N39" s="121" t="str"/>
+      <c r="O39" s="123" t="str"/>
+      <c r="P39" s="124"/>
+      <c r="Q39" s="113"/>
+      <c r="R39" s="113"/>
+      <c r="S39" s="113"/>
+      <c r="T39" s="113"/>
+      <c r="U39" s="113"/>
+      <c r="V39" s="113"/>
+      <c r="W39" s="113"/>
+      <c r="X39" s="113"/>
+      <c r="Y39" s="113"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
@@ -3952,6 +4026,7 @@
     <mergeCell ref="A32:O32"/>
     <mergeCell ref="A34:O34"/>
     <mergeCell ref="A36:O36"/>
+    <mergeCell ref="A38:O38"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.9840277777777777" footer="0.0" header="0.0" left="0.7479166666666667" right="0.25" top="0.75"/>
@@ -5388,7 +5463,7 @@
         <v>Number of TCs</v>
       </c>
       <c r="B4" s="111" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -5460,19 +5535,19 @@
         <v>Round 1</v>
       </c>
       <c r="B6" s="115" t="n">
-        <f>COUNTIF(F12:F16,"Passed")</f>
+        <f>COUNTIF(F12:F21,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C6" s="115" t="n">
-        <f>COUNTIF(F12:F16,"Failed")</f>
+        <f>COUNTIF(F12:F21,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D6" s="115" t="n">
         <f>B4-B6-C6-E6</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" s="115" t="n">
-        <f>COUNTIF(F12:F16,"Skipped")</f>
+        <f>COUNTIF(F12:F21,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F6" s="108"/>
@@ -5501,19 +5576,19 @@
         <v>Round 2</v>
       </c>
       <c r="B7" s="115" t="n">
-        <f>COUNTIF(I12:I16,"Passed")</f>
+        <f>COUNTIF(I12:I21,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C7" s="115" t="n">
-        <f>COUNTIF(I12:I16,"Failed")</f>
+        <f>COUNTIF(I12:I21,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D7" s="115" t="n">
         <f>B4-B7-C7-E7</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="115" t="n">
-        <f>COUNTIF(I12:I16,"Skipped")</f>
+        <f>COUNTIF(I12:I21,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F7" s="108"/>
@@ -5542,19 +5617,19 @@
         <v>Round 3</v>
       </c>
       <c r="B8" s="115" t="n">
-        <f>COUNTIF(L12:L16,"Passed")</f>
+        <f>COUNTIF(L12:L21,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C8" s="115" t="n">
-        <f>COUNTIF(L12:L16,"Failed")</f>
+        <f>COUNTIF(L12:L21,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D8" s="115" t="n">
         <f>B4-B8-C8-E8</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="115" t="n">
-        <f>COUNTIF(L12:L16,"Skipped")</f>
+        <f>COUNTIF(L12:L21,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F8" s="108"/>
@@ -5691,26 +5766,31 @@
       <c r="X11" s="113"/>
       <c r="Y11" s="113"/>
     </row>
-    <row r="12" ht="182.0" customHeight="1">
+    <row r="12" ht="298.0" customHeight="1">
       <c r="A12" s="121" t="str">
         <v>REC_FT01</v>
       </c>
       <c r="B12" s="121" t="str">
-        <v>The Secretary records or uploads a recording with consent and gets a transcript.</v>
+        <v>The Secretary records the room with the room mic, or uploads a file, with consent, and gets a transcript.</v>
       </c>
       <c r="C12" s="121" t="str">
-        <v>1. Open tab "Bản ghi" during the meeting.
-2. Click "Bắt đầu ghi âm", enter Mục đích ghi âm "Lập biên bản cuộc họp", tick the consent statement and click "Bắt đầu ghi"; later stop and save ("Lưu tệp ghi âm").
-3. Or click "Tải tệp ghi âm lên" and choose an audio file.
-4. Open "Nghe và xem bản gỡ băng".</v>
+        <v>1. Open tab "Bản ghi" of an in-person meeting during the meeting.
+2. In the mic card click "Bật mic phòng"; in "Bắt đầu ghi âm" enter Mục đích ghi âm "Lập biên bản cuộc họp", tick the statement that participants were told and click "Bắt đầu ghi".
+3. Speak for a while, then click "Tắt mic, lưu lượt ghi".
+4. Switch the mic on and off again for a second take.
+5. Or click "Tải tệp lên", choose an audio file and confirm "Tải lên" in "Lưu tệp ghi âm".
+6. Open "Nghe và xem bản gỡ băng".</v>
       </c>
       <c r="D12" s="121" t="str">
-        <v>1. "Đã lưu bản ghi." appears; the recording shows Ghi trực tiếp or Tải lên and "Đang chuyển chữ".
-2. When done it shows "Có bản gỡ băng"; the transcript lists speakers and times.
-3. Without ticking consent the recording cannot start.</v>
+        <v>1. While recording the card shows "Đang ghi cả phòng" and the list shows "Mic phòng đang ghi" to everyone.
+2. Switching off shows "Đã lưu lượt ghi."; the recording shows Mic phòng and "Đang chuyển chữ".
+3. The second take needs no new consent and is appended to the same recording, which is transcribed again.
+4. An uploaded file shows Tải lên.
+5. When done it shows "Có bản gỡ băng"; the transcript lists speakers and times.
+6. Without ticking consent the mic cannot start; an Online meeting has no room mic.</v>
       </c>
       <c r="E12" s="121" t="str">
-        <v>1. An InProgress meeting; signed in as its Secretary; speech worker running.</v>
+        <v>1. An InProgress in-person meeting; signed in as its Secretary; microphone allowed; speech worker running.</v>
       </c>
       <c r="F12" s="121" t="str">
         <v>Pending</v>
@@ -5777,7 +5857,7 @@
       <c r="X13" s="113"/>
       <c r="Y13" s="113"/>
     </row>
-    <row r="14" ht="66.0" customHeight="1">
+    <row r="14" ht="80.5" customHeight="1">
       <c r="A14" s="121" t="str">
         <v>REC_FT03</v>
       </c>
@@ -5788,7 +5868,8 @@
         <v>1. Click "Xoá bản ghi" and confirm.</v>
       </c>
       <c r="D14" s="121" t="str">
-        <v>1. "Đã xoá bản ghi." appears; the audio and its transcript are erased; the row shows Đã xoá and can no longer be played.</v>
+        <v>1. "Xoá bản ghi?" is asked first.
+2. "Đã xoá bản ghi." appears; the recording leaves the tab and can no longer be played; its audio and transcript are erased.</v>
       </c>
       <c r="E14" s="121" t="str">
         <v>1. A stored recording; signed in as the Secretary.</v>
@@ -5845,24 +5926,26 @@
       <c r="X15" s="113"/>
       <c r="Y15" s="113"/>
     </row>
-    <row r="16" ht="95.0" customHeight="1">
+    <row r="16" ht="138.5" customHeight="1">
       <c r="A16" s="121" t="str">
         <v>REC_FT04</v>
       </c>
       <c r="B16" s="121" t="str">
-        <v>Per-microphone capture turns each participant's sentences into text.</v>
+        <v>In an online meeting each participant's microphone turns their sentences into text and audio.</v>
       </c>
       <c r="C16" s="121" t="str">
-        <v>1. In a per-microphone meeting room, open Lời nói and click "Ghi lời tôi".
+        <v>1. Join the room of an InProgress Online meeting and turn the microphone on.
 2. Say a sentence and pause.
-3. Delete one of your sentences ("Xoá câu này").</v>
+3. Open "Ghi âm của tôi" and play the sentence back ("Nghe lại").
+4. Click "Xoá câu này" and confirm "Xoá câu".</v>
       </c>
       <c r="D16" s="121" t="str">
-        <v>1. The status shows "Đang ghi"; each sentence appears as text under your name.
-2. Deleting shows "Đã xoá câu nói." and the sentence leaves the transcript.</v>
+        <v>1. The room shows "Cuộc họp được ghi âm để lập biên bản · tự xoá sau 180 ngày" and "Đang ghi lời bạn".
+2. Each sentence appears as text under "Micro của &lt;name&gt;" in tab "Bản ghi" and can be heard back.
+3. Deleting shows "Đã xoá câu nói." and the sentence and its audio leave the meeting.</v>
       </c>
       <c r="E16" s="121" t="str">
-        <v>1. An InProgress meeting whose Cách ghi âm is per microphone; speech worker running.</v>
+        <v>1. An InProgress Online (or Hybrid) meeting; signed in as a participant; microphone allowed; speech worker running.</v>
       </c>
       <c r="F16" s="121" t="str">
         <v>Pending</v>
@@ -5887,13 +5970,204 @@
       <c r="X16" s="113"/>
       <c r="Y16" s="113"/>
     </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="121" t="str">
+        <v>Bản ghi</v>
+      </c>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="113"/>
+      <c r="S17" s="113"/>
+      <c r="T17" s="113"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="113"/>
+      <c r="W17" s="113"/>
+      <c r="X17" s="113"/>
+      <c r="Y17" s="113"/>
+    </row>
+    <row r="18" ht="138.5" customHeight="1">
+      <c r="A18" s="121" t="str">
+        <v>REC_FT05</v>
+      </c>
+      <c r="B18" s="121" t="str">
+        <v>The Secretary deletes one take of the room recording.</v>
+      </c>
+      <c r="C18" s="121" t="str">
+        <v>1. Open the transcript of a room recording with several takes.
+2. On one take click "Xoá lượt này" and confirm "Xoá lượt".</v>
+      </c>
+      <c r="D18" s="121" t="str">
+        <v>1. The dialog warns the take's sound and words are removed for good.
+2. "Đã xoá lượt ghi." appears; the take's lines leave the transcript, later lines move up, corrected text and assigned names stay.
+3. With only one take left, deleting it is refused: delete the whole recording instead.</v>
+      </c>
+      <c r="E18" s="121" t="str">
+        <v>1. A room recording with at least two takes and a completed transcript; signed in as its Secretary.</v>
+      </c>
+      <c r="F18" s="121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G18" s="122" t="str"/>
+      <c r="H18" s="121" t="str"/>
+      <c r="I18" s="121" t="str"/>
+      <c r="J18" s="122" t="str"/>
+      <c r="K18" s="121" t="str"/>
+      <c r="L18" s="121" t="str"/>
+      <c r="M18" s="122" t="str"/>
+      <c r="N18" s="121" t="str"/>
+      <c r="O18" s="123" t="str"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="113"/>
+      <c r="R18" s="113"/>
+      <c r="S18" s="113"/>
+      <c r="T18" s="113"/>
+      <c r="U18" s="113"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="113"/>
+      <c r="X18" s="113"/>
+      <c r="Y18" s="113"/>
+    </row>
+    <row r="19" ht="138.5" customHeight="1">
+      <c r="A19" s="121" t="str">
+        <v>REC_FT06</v>
+      </c>
+      <c r="B19" s="121" t="str">
+        <v>The Chair or Secretary saves the recording and the transcript to the computer.</v>
+      </c>
+      <c r="C19" s="121" t="str">
+        <v>1. On a recording click "Tải tệp ghi âm".
+2. In the transcript click "Tải bản gỡ băng (.txt)".
+3. For an Online meeting click "Tải lời thoại (.txt)".
+4. Sign in as thanhvien and open the same meeting.</v>
+      </c>
+      <c r="D19" s="121" t="str">
+        <v>1. The original audio file and a text transcript with names and times are downloaded.
+2. The per-microphone text leaves out sentences taken out of the record.
+3. thanhvien sees no download buttons.
+4. For a Mật meeting nobody can download.</v>
+      </c>
+      <c r="E19" s="121" t="str">
+        <v>1. An Internal meeting with a transcribed recording; signed in as chutoa or thuky.</v>
+      </c>
+      <c r="F19" s="121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G19" s="122" t="str"/>
+      <c r="H19" s="121" t="str"/>
+      <c r="I19" s="121" t="str"/>
+      <c r="J19" s="122" t="str"/>
+      <c r="K19" s="121" t="str"/>
+      <c r="L19" s="121" t="str"/>
+      <c r="M19" s="122" t="str"/>
+      <c r="N19" s="121" t="str"/>
+      <c r="O19" s="123" t="str"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="113"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="113"/>
+      <c r="T19" s="113"/>
+      <c r="U19" s="113"/>
+      <c r="V19" s="113"/>
+      <c r="W19" s="113"/>
+      <c r="X19" s="113"/>
+      <c r="Y19" s="113"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="121" t="str">
+        <v>Lời nói</v>
+      </c>
+      <c r="B20" s="121"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="121"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="113"/>
+      <c r="R20" s="113"/>
+      <c r="S20" s="113"/>
+      <c r="T20" s="113"/>
+      <c r="U20" s="113"/>
+      <c r="V20" s="113"/>
+      <c r="W20" s="113"/>
+      <c r="X20" s="113"/>
+      <c r="Y20" s="113"/>
+    </row>
+    <row r="21" ht="167.5" customHeight="1">
+      <c r="A21" s="121" t="str">
+        <v>REC_FT07</v>
+      </c>
+      <c r="B21" s="121" t="str">
+        <v>The Chair or Secretary takes a sentence out of the record and puts it back.</v>
+      </c>
+      <c r="C21" s="121" t="str">
+        <v>1. In tab "Bản ghi" of an Online meeting, on a sentence click "Bỏ khỏi biên bản".
+2. Sign in as thanhvien and look at the same sentence.
+3. As the Chair click "Khôi phục".</v>
+      </c>
+      <c r="D21" s="121" t="str">
+        <v>1. "Đã loại câu khỏi bản ghi." appears; the Chair still sees the words marked as left out.
+2. thanhvien sees "Câu đã được bỏ khỏi biên bản." without the words or audio.
+3. Restoring shows "Đã đưa câu trở lại bản ghi.".
+4. A quieter copy of another person's sentence is highlighted as possibly theirs.</v>
+      </c>
+      <c r="E21" s="121" t="str">
+        <v>1. An Online meeting with stored sentences; signed in as chutoa.</v>
+      </c>
+      <c r="F21" s="121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G21" s="122" t="str"/>
+      <c r="H21" s="121" t="str"/>
+      <c r="I21" s="121" t="str"/>
+      <c r="J21" s="122" t="str"/>
+      <c r="K21" s="121" t="str"/>
+      <c r="L21" s="121" t="str"/>
+      <c r="M21" s="122" t="str"/>
+      <c r="N21" s="121" t="str"/>
+      <c r="O21" s="123" t="str"/>
+      <c r="P21" s="124"/>
+      <c r="Q21" s="113"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="113"/>
+      <c r="T21" s="113"/>
+      <c r="U21" s="113"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="113"/>
+      <c r="X21" s="113"/>
+      <c r="Y21" s="113"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="A11:O11"/>
     <mergeCell ref="A15:O15"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A20:O20"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.9840277777777777" footer="0.0" header="0.0" left="0.7479166666666667" right="0.25" top="0.75"/>
@@ -7495,7 +7769,7 @@
         <v>Number of TCs</v>
       </c>
       <c r="B4" s="111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -7567,19 +7841,19 @@
         <v>Round 1</v>
       </c>
       <c r="B6" s="115" t="n">
-        <f>COUNTIF(F12:F14,"Passed")</f>
+        <f>COUNTIF(F12:F15,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C6" s="115" t="n">
-        <f>COUNTIF(F12:F14,"Failed")</f>
+        <f>COUNTIF(F12:F15,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D6" s="115" t="n">
         <f>B4-B6-C6-E6</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="115" t="n">
-        <f>COUNTIF(F12:F14,"Skipped")</f>
+        <f>COUNTIF(F12:F15,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F6" s="108"/>
@@ -7608,19 +7882,19 @@
         <v>Round 2</v>
       </c>
       <c r="B7" s="115" t="n">
-        <f>COUNTIF(I12:I14,"Passed")</f>
+        <f>COUNTIF(I12:I15,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C7" s="115" t="n">
-        <f>COUNTIF(I12:I14,"Failed")</f>
+        <f>COUNTIF(I12:I15,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D7" s="115" t="n">
         <f>B4-B7-C7-E7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="115" t="n">
-        <f>COUNTIF(I12:I14,"Skipped")</f>
+        <f>COUNTIF(I12:I15,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F7" s="108"/>
@@ -7649,19 +7923,19 @@
         <v>Round 3</v>
       </c>
       <c r="B8" s="115" t="n">
-        <f>COUNTIF(L12:L14,"Passed")</f>
+        <f>COUNTIF(L12:L15,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C8" s="115" t="n">
-        <f>COUNTIF(L12:L14,"Failed")</f>
+        <f>COUNTIF(L12:L15,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D8" s="115" t="n">
         <f>B4-B8-C8-E8</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="115" t="n">
-        <f>COUNTIF(L12:L14,"Skipped")</f>
+        <f>COUNTIF(L12:L15,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F8" s="108"/>
@@ -7798,7 +8072,7 @@
       <c r="X11" s="113"/>
       <c r="Y11" s="113"/>
     </row>
-    <row r="12" ht="138.5" customHeight="1">
+    <row r="12" ht="153.0" customHeight="1">
       <c r="A12" s="121" t="str">
         <v>VOICE_FT01</v>
       </c>
@@ -7813,7 +8087,8 @@
       <c r="D12" s="121" t="str">
         <v>1. Without ticking, Voice ID cannot be turned on.
 2. After consent the status is "Đang bật".
-3. Each good sample is listed; a bad one (noise, two voices) is refused with the reason.</v>
+3. Each good sample is listed; a bad one (noise, two voices) is refused with the reason.
+4. Each new sample can be played back ("Nghe lại"); only its owner hears it.</v>
       </c>
       <c r="E12" s="121" t="str">
         <v>1. Microphone allowed; speech worker running.</v>
@@ -7921,6 +8196,49 @@
       <c r="W14" s="113"/>
       <c r="X14" s="113"/>
       <c r="Y14" s="113"/>
+    </row>
+    <row r="15" ht="124.0" customHeight="1">
+      <c r="A15" s="121" t="str">
+        <v>VOICE_FT04</v>
+      </c>
+      <c r="B15" s="121" t="str">
+        <v>Someone who agreed to the earlier notice renews to keep new sample recordings.</v>
+      </c>
+      <c r="C15" s="121" t="str">
+        <v>1. Open Giọng nói của tôi.
+2. Read the notice about the new terms and click "Đồng ý điều khoản mới".
+3. Record a new sample and play it back.</v>
+      </c>
+      <c r="D15" s="121" t="str">
+        <v>1. The page explains that from now on the sample recording is kept, encrypted, for the owner to hear; old samples stay but cannot be played.
+2. After renewing, "Đã bật nhận diện giọng nói cho tài khoản của bạn." appears and the existing samples stay.
+3. The new sample has "Nghe lại".</v>
+      </c>
+      <c r="E15" s="121" t="str">
+        <v>1. A user who turned Voice ID on under the earlier notice and has samples.</v>
+      </c>
+      <c r="F15" s="121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G15" s="122" t="str"/>
+      <c r="H15" s="121" t="str"/>
+      <c r="I15" s="121" t="str"/>
+      <c r="J15" s="122" t="str"/>
+      <c r="K15" s="121" t="str"/>
+      <c r="L15" s="121" t="str"/>
+      <c r="M15" s="122" t="str"/>
+      <c r="N15" s="121" t="str"/>
+      <c r="O15" s="123" t="str"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="113"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="113"/>
+      <c r="T15" s="113"/>
+      <c r="U15" s="113"/>
+      <c r="V15" s="113"/>
+      <c r="W15" s="113"/>
+      <c r="X15" s="113"/>
+      <c r="Y15" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8215,7 +8533,7 @@
         <v>Agenda</v>
       </c>
       <c r="E9" s="63" t="str">
-        <v>6 definitions / scenarios</v>
+        <v>7 definitions / scenarios</v>
       </c>
       <c r="F9" s="64" t="str">
         <v>See the Pre-conditions of each case.</v>
@@ -8481,7 +8799,7 @@
         <v>Meetings</v>
       </c>
       <c r="E16" s="63" t="str">
-        <v>17 definitions / scenarios</v>
+        <v>18 definitions / scenarios</v>
       </c>
       <c r="F16" s="64" t="str">
         <v>See the Pre-conditions of each case.</v>
@@ -8595,7 +8913,7 @@
         <v>Recordings</v>
       </c>
       <c r="E19" s="63" t="str">
-        <v>4 definitions / scenarios</v>
+        <v>7 definitions / scenarios</v>
       </c>
       <c r="F19" s="64" t="str">
         <v>See the Pre-conditions of each case.</v>
@@ -8709,7 +9027,7 @@
         <v>Voice ID</v>
       </c>
       <c r="E22" s="63" t="str">
-        <v>3 definitions / scenarios</v>
+        <v>4 definitions / scenarios</v>
       </c>
       <c r="F22" s="64" t="str">
         <v>See the Pre-conditions of each case.</v>
@@ -8921,7 +9239,7 @@
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="78" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="10"/>
@@ -9117,7 +9435,7 @@
       </c>
       <c r="F11" s="89" t="n">
         <f>'Agenda'!D6</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="89" t="n">
         <f>'Agenda'!E6</f>
@@ -9125,7 +9443,7 @@
       </c>
       <c r="H11" s="91" t="n">
         <f>'Agenda'!B4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="44"/>
       <c r="J11" s="10"/>
@@ -9446,7 +9764,7 @@
       </c>
       <c r="F18" s="89" t="n">
         <f>'Meetings'!D6</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="89" t="n">
         <f>'Meetings'!E6</f>
@@ -9454,7 +9772,7 @@
       </c>
       <c r="H18" s="91" t="n">
         <f>'Meetings'!B4</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="44"/>
       <c r="J18" s="10"/>
@@ -9587,7 +9905,7 @@
       </c>
       <c r="F21" s="89" t="n">
         <f>'Recordings'!D6</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" s="89" t="n">
         <f>'Recordings'!E6</f>
@@ -9595,7 +9913,7 @@
       </c>
       <c r="H21" s="91" t="n">
         <f>'Recordings'!B4</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I21" s="44"/>
       <c r="J21" s="10"/>
@@ -9728,7 +10046,7 @@
       </c>
       <c r="F24" s="89" t="n">
         <f>'Voice ID'!D6</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="89" t="n">
         <f>'Voice ID'!E6</f>
@@ -9736,7 +10054,7 @@
       </c>
       <c r="H24" s="91" t="n">
         <f>'Voice ID'!B4</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="44"/>
       <c r="J24" s="10"/>
@@ -9773,7 +10091,7 @@
       </c>
       <c r="F25" s="94" t="n">
         <f>SUM(F11:F24)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G25" s="94" t="n">
         <f>SUM(G11:G24)</f>
@@ -9781,7 +10099,7 @@
       </c>
       <c r="H25" s="95" t="n">
         <f>SUM(H11:H24)</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I25" s="44"/>
       <c r="J25" s="10"/>
@@ -10040,7 +10358,7 @@
         <v>Number of TCs</v>
       </c>
       <c r="B4" s="111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -10112,19 +10430,19 @@
         <v>Round 1</v>
       </c>
       <c r="B6" s="115" t="n">
-        <f>COUNTIF(F12:F17,"Passed")</f>
+        <f>COUNTIF(F12:F18,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C6" s="115" t="n">
-        <f>COUNTIF(F12:F17,"Failed")</f>
+        <f>COUNTIF(F12:F18,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D6" s="115" t="n">
         <f>B4-B6-C6-E6</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="115" t="n">
-        <f>COUNTIF(F12:F17,"Skipped")</f>
+        <f>COUNTIF(F12:F18,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F6" s="108"/>
@@ -10153,19 +10471,19 @@
         <v>Round 2</v>
       </c>
       <c r="B7" s="115" t="n">
-        <f>COUNTIF(I12:I17,"Passed")</f>
+        <f>COUNTIF(I12:I18,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C7" s="115" t="n">
-        <f>COUNTIF(I12:I17,"Failed")</f>
+        <f>COUNTIF(I12:I18,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D7" s="115" t="n">
         <f>B4-B7-C7-E7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" s="115" t="n">
-        <f>COUNTIF(I12:I17,"Skipped")</f>
+        <f>COUNTIF(I12:I18,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F7" s="108"/>
@@ -10194,19 +10512,19 @@
         <v>Round 3</v>
       </c>
       <c r="B8" s="115" t="n">
-        <f>COUNTIF(L12:L17,"Passed")</f>
+        <f>COUNTIF(L12:L18,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C8" s="115" t="n">
-        <f>COUNTIF(L12:L17,"Failed")</f>
+        <f>COUNTIF(L12:L18,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D8" s="115" t="n">
         <f>B4-B8-C8-E8</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="115" t="n">
-        <f>COUNTIF(L12:L17,"Skipped")</f>
+        <f>COUNTIF(L12:L18,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="F8" s="108"/>
@@ -10352,7 +10670,7 @@
       </c>
       <c r="C12" s="121" t="str">
         <v>1. Open tab "Nội dung cuộc họp" and click "Thêm nội dung".
-2. Enter Nội dung cần bàn: Dự toán ngân sách năm 2027, choose Người trình bày and a document, click Lưu.
+2. Enter Nội dung cần bàn: Dự toán ngân sách năm 2027, choose Người trình bày, click Lưu.
 3. Add two more items and drag one to a new position ("Kéo để đổi vị trí").
 4. Edit an item ("Sửa"), then delete one ("Xoá nội dung").</v>
       </c>
@@ -10593,6 +10911,51 @@
       <c r="W17" s="113"/>
       <c r="X17" s="113"/>
       <c r="Y17" s="113"/>
+    </row>
+    <row r="18" ht="196.5" customHeight="1">
+      <c r="A18" s="121" t="str">
+        <v>AGD_FT07</v>
+      </c>
+      <c r="B18" s="121" t="str">
+        <v>The Chair or Secretary adds documents to an agenda item from its paperclip.</v>
+      </c>
+      <c r="C18" s="121" t="str">
+        <v>1. On an agenda item click the paperclip ("Thêm tài liệu").
+2. Choose "Chọn từ tài liệu cuộc họp", tick a document and click "Gắn 1 tài liệu".
+3. Open the paperclip again, choose "Tải tệp lên từ máy" and add a PDF; then "Chọn từ kho của tôi" and add a library document.
+4. Sign in as thanhvien and open the agenda.</v>
+      </c>
+      <c r="D18" s="121" t="str">
+        <v>1. The dialog "Thêm tài liệu cho mục 1" opens on the chosen source.
+2. "Đã gắn tài liệu vào mục nghị sự." appears and the documents show under the item.
+3. An uploaded or library document is also added to the meeting's documents.
+4. thanhvien sees the documents but no paperclip; after the meeting ends nobody can add documents.</v>
+      </c>
+      <c r="E18" s="121" t="str">
+        <v>1. A Published or InProgress meeting with agenda items and documents; signed in as chutoa or thuky.</v>
+      </c>
+      <c r="F18" s="121" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G18" s="122" t="str"/>
+      <c r="H18" s="121" t="str"/>
+      <c r="I18" s="121" t="str"/>
+      <c r="J18" s="122" t="str"/>
+      <c r="K18" s="121" t="str"/>
+      <c r="L18" s="121" t="str"/>
+      <c r="M18" s="122" t="str"/>
+      <c r="N18" s="121" t="str"/>
+      <c r="O18" s="123" t="str"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="113"/>
+      <c r="R18" s="113"/>
+      <c r="S18" s="113"/>
+      <c r="T18" s="113"/>
+      <c r="U18" s="113"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="113"/>
+      <c r="X18" s="113"/>
+      <c r="Y18" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/docs/08-reports/test-reports/Report5.2_Integration_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.2_Integration_Test.xlsx
@@ -36,61 +36,60 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="MS PGothic"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="26.0"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="20.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font/>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF993300"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF008000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -100,99 +99,98 @@
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="MS PGothic"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF0000FF"/>
-      <name val="MS PGothic"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
       <sz val="10.0"/>
       <color rgb="FF0000FF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF0000FF"/>
-      <name val="MS PGothic"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF0000FF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="MS PGothic"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1114,14 +1112,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="MS PGothic"/>
-        <a:ea typeface="MS PGothic"/>
-        <a:cs typeface="MS PGothic"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="MS PGothic"/>
-        <a:ea typeface="MS PGothic"/>
-        <a:cs typeface="MS PGothic"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
